--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T08:50:20+00:00</t>
+    <t>2023-05-10T08:50:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T08:50:38+00:00</t>
+    <t>2023-05-10T09:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:32+00:00</t>
+    <t>2023-05-10T09:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:57+00:00</t>
+    <t>2023-05-10T09:45:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:45:15+00:00</t>
+    <t>2023-05-10T09:50:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:50:54+00:00</t>
+    <t>2023-05-10T10:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:15:35+00:00</t>
+    <t>2023-05-10T10:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:16:16+00:00</t>
+    <t>2023-05-10T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:21+00:00</t>
+    <t>2023-05-10T11:05:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:55+00:00</t>
+    <t>2023-05-10T11:27:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:27:56+00:00</t>
+    <t>2023-05-10T11:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:35:39+00:00</t>
+    <t>2023-05-10T12:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:05+00:00</t>
+    <t>2023-05-10T12:21:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:34+00:00</t>
+    <t>2023-05-11T06:47:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:47:47+00:00</t>
+    <t>2023-05-11T06:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:48:00+00:00</t>
+    <t>2023-05-11T06:54:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:54:20+00:00</t>
+    <t>2023-05-11T06:54:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:54:25+00:00</t>
+    <t>2023-05-11T08:35:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -505,7 +505,7 @@
     <t>Id for specimen.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:system}
+    <t xml:space="preserve">exists:system}
 </t>
   </si>
   <si>
@@ -5285,7 +5285,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>85</v>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>85</v>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>85</v>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:35:45+00:00</t>
+    <t>2023-05-11T08:41:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:41:43+00:00</t>
+    <t>2023-05-11T09:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -505,7 +505,7 @@
     <t>Id for specimen.</t>
   </si>
   <si>
-    <t xml:space="preserve">exists:system}
+    <t xml:space="preserve">value:system}
 </t>
   </si>
   <si>
@@ -5285,7 +5285,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>85</v>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>85</v>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>85</v>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:08:26+00:00</t>
+    <t>2023-05-11T09:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4327" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4328" uniqueCount="577">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:17:12+00:00</t>
+    <t>2023-05-11T10:17:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -507,6 +507,9 @@
   <si>
     <t xml:space="preserve">value:system}
 </t>
+  </si>
+  <si>
+    <t>Slice based on the type of identifier.</t>
   </si>
   <si>
     <t>openAtEnd</t>
@@ -3458,12 +3461,14 @@
       <c r="AB12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AC12" s="2"/>
+      <c r="AC12" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="AD12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AF12" t="s" s="2">
         <v>151</v>
@@ -3481,24 +3486,24 @@
         <v>97</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>151</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>76</v>
@@ -3592,21 +3597,21 @@
         <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3632,10 +3637,10 @@
         <v>87</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3686,7 +3691,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3695,7 +3700,7 @@
         <v>85</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>76</v>
@@ -3704,7 +3709,7 @@
         <v>76</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>76</v>
@@ -3712,10 +3717,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3741,10 +3746,10 @@
         <v>132</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N15" t="s" s="2">
         <v>148</v>
@@ -3788,7 +3793,7 @@
         <v>135</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>76</v>
@@ -3797,7 +3802,7 @@
         <v>136</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3815,7 +3820,7 @@
         <v>76</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>76</v>
@@ -3823,10 +3828,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3852,16 +3857,16 @@
         <v>105</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>76</v>
@@ -3889,10 +3894,10 @@
         <v>109</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>76</v>
@@ -3910,7 +3915,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3928,7 +3933,7 @@
         <v>76</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>130</v>
@@ -3936,10 +3941,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3962,19 +3967,19 @@
         <v>86</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>76</v>
@@ -3999,13 +4004,13 @@
         <v>76</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>76</v>
@@ -4023,7 +4028,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -4041,18 +4046,18 @@
         <v>76</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4078,10 +4083,10 @@
         <v>87</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4132,7 +4137,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -4141,7 +4146,7 @@
         <v>85</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>76</v>
@@ -4150,7 +4155,7 @@
         <v>76</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>76</v>
@@ -4158,10 +4163,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4187,10 +4192,10 @@
         <v>132</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>148</v>
@@ -4234,7 +4239,7 @@
         <v>135</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>76</v>
@@ -4243,7 +4248,7 @@
         <v>136</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -4261,7 +4266,7 @@
         <v>76</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>76</v>
@@ -4269,10 +4274,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4295,19 +4300,19 @@
         <v>86</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -4356,7 +4361,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -4374,18 +4379,18 @@
         <v>76</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4411,10 +4416,10 @@
         <v>87</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4465,7 +4470,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -4474,7 +4479,7 @@
         <v>85</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>76</v>
@@ -4483,7 +4488,7 @@
         <v>76</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>76</v>
@@ -4491,10 +4496,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4520,10 +4525,10 @@
         <v>132</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>148</v>
@@ -4567,7 +4572,7 @@
         <v>135</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>76</v>
@@ -4576,7 +4581,7 @@
         <v>136</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4594,7 +4599,7 @@
         <v>76</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>76</v>
@@ -4602,10 +4607,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4631,16 +4636,16 @@
         <v>99</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>76</v>
@@ -4650,7 +4655,7 @@
         <v>76</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>76</v>
@@ -4689,7 +4694,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4707,18 +4712,18 @@
         <v>76</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4741,16 +4746,16 @@
         <v>86</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4800,7 +4805,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4818,18 +4823,18 @@
         <v>76</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4855,14 +4860,14 @@
         <v>105</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4872,7 +4877,7 @@
         <v>76</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>76</v>
@@ -4911,7 +4916,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4920,7 +4925,7 @@
         <v>85</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>97</v>
@@ -4929,18 +4934,18 @@
         <v>76</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4963,17 +4968,17 @@
         <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>76</v>
@@ -4983,7 +4988,7 @@
         <v>76</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>76</v>
@@ -5022,7 +5027,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -5031,7 +5036,7 @@
         <v>85</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>97</v>
@@ -5040,18 +5045,18 @@
         <v>76</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5074,19 +5079,19 @@
         <v>86</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -5135,7 +5140,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -5153,18 +5158,18 @@
         <v>76</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5187,19 +5192,19 @@
         <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>76</v>
@@ -5209,7 +5214,7 @@
         <v>76</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>76</v>
@@ -5248,7 +5253,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -5266,18 +5271,18 @@
         <v>76</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5303,29 +5308,29 @@
         <v>99</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>76</v>
@@ -5361,7 +5366,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -5379,18 +5384,18 @@
         <v>76</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5413,16 +5418,16 @@
         <v>86</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5436,7 +5441,7 @@
         <v>76</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>76</v>
@@ -5472,7 +5477,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5481,7 +5486,7 @@
         <v>85</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>97</v>
@@ -5490,18 +5495,18 @@
         <v>76</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5524,13 +5529,13 @@
         <v>86</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5581,7 +5586,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5599,18 +5604,18 @@
         <v>76</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5633,16 +5638,16 @@
         <v>86</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5692,7 +5697,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5710,21 +5715,21 @@
         <v>76</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>151</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>76</v>
@@ -5818,21 +5823,21 @@
         <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5858,10 +5863,10 @@
         <v>87</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5912,7 +5917,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5921,7 +5926,7 @@
         <v>85</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>76</v>
@@ -5930,7 +5935,7 @@
         <v>76</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>76</v>
@@ -5938,10 +5943,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5967,10 +5972,10 @@
         <v>132</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>148</v>
@@ -6014,7 +6019,7 @@
         <v>135</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>76</v>
@@ -6023,7 +6028,7 @@
         <v>136</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -6041,7 +6046,7 @@
         <v>76</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>76</v>
@@ -6049,10 +6054,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6078,16 +6083,16 @@
         <v>105</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>76</v>
@@ -6115,10 +6120,10 @@
         <v>109</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>76</v>
@@ -6136,7 +6141,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -6154,7 +6159,7 @@
         <v>76</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>130</v>
@@ -6162,10 +6167,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6188,19 +6193,19 @@
         <v>86</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>76</v>
@@ -6225,13 +6230,13 @@
         <v>76</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>76</v>
@@ -6249,7 +6254,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -6267,18 +6272,18 @@
         <v>76</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6304,10 +6309,10 @@
         <v>87</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6358,7 +6363,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6367,7 +6372,7 @@
         <v>85</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>76</v>
@@ -6376,7 +6381,7 @@
         <v>76</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>76</v>
@@ -6384,10 +6389,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6413,10 +6418,10 @@
         <v>132</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>148</v>
@@ -6460,7 +6465,7 @@
         <v>135</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>76</v>
@@ -6469,7 +6474,7 @@
         <v>136</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6487,7 +6492,7 @@
         <v>76</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>76</v>
@@ -6495,10 +6500,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6521,19 +6526,19 @@
         <v>86</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>76</v>
@@ -6582,7 +6587,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6600,18 +6605,18 @@
         <v>76</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6637,10 +6642,10 @@
         <v>87</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6691,7 +6696,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6700,7 +6705,7 @@
         <v>85</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>76</v>
@@ -6709,7 +6714,7 @@
         <v>76</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>76</v>
@@ -6717,10 +6722,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6746,10 +6751,10 @@
         <v>132</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>148</v>
@@ -6793,7 +6798,7 @@
         <v>135</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>76</v>
@@ -6802,7 +6807,7 @@
         <v>136</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6820,7 +6825,7 @@
         <v>76</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>76</v>
@@ -6828,10 +6833,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6857,16 +6862,16 @@
         <v>99</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>76</v>
@@ -6876,7 +6881,7 @@
         <v>76</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>76</v>
@@ -6915,7 +6920,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6933,18 +6938,18 @@
         <v>76</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6967,16 +6972,16 @@
         <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7026,7 +7031,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -7044,18 +7049,18 @@
         <v>76</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7081,14 +7086,14 @@
         <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>76</v>
@@ -7098,7 +7103,7 @@
         <v>76</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>76</v>
@@ -7137,7 +7142,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -7146,7 +7151,7 @@
         <v>85</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>97</v>
@@ -7155,18 +7160,18 @@
         <v>76</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7189,17 +7194,17 @@
         <v>86</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -7209,7 +7214,7 @@
         <v>76</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>76</v>
@@ -7248,7 +7253,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -7257,7 +7262,7 @@
         <v>85</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>97</v>
@@ -7266,18 +7271,18 @@
         <v>76</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7300,19 +7305,19 @@
         <v>86</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>76</v>
@@ -7361,7 +7366,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -7379,18 +7384,18 @@
         <v>76</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7413,19 +7418,19 @@
         <v>86</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>76</v>
@@ -7435,7 +7440,7 @@
         <v>76</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="T48" t="s" s="2">
         <v>76</v>
@@ -7474,7 +7479,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7492,18 +7497,18 @@
         <v>76</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7529,29 +7534,29 @@
         <v>99</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>76</v>
@@ -7587,7 +7592,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7605,18 +7610,18 @@
         <v>76</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7639,16 +7644,16 @@
         <v>86</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7662,7 +7667,7 @@
         <v>76</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>76</v>
@@ -7698,7 +7703,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7707,7 +7712,7 @@
         <v>85</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>97</v>
@@ -7716,18 +7721,18 @@
         <v>76</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7750,13 +7755,13 @@
         <v>86</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7807,7 +7812,7 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7825,18 +7830,18 @@
         <v>76</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7859,16 +7864,16 @@
         <v>86</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7918,7 +7923,7 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7936,21 +7941,21 @@
         <v>76</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>151</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>76</v>
@@ -8044,21 +8049,21 @@
         <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8084,10 +8089,10 @@
         <v>87</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8138,7 +8143,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -8147,7 +8152,7 @@
         <v>85</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>76</v>
@@ -8156,7 +8161,7 @@
         <v>76</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>76</v>
@@ -8164,10 +8169,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8193,10 +8198,10 @@
         <v>132</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>148</v>
@@ -8240,7 +8245,7 @@
         <v>135</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>76</v>
@@ -8249,7 +8254,7 @@
         <v>136</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -8267,7 +8272,7 @@
         <v>76</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>76</v>
@@ -8275,10 +8280,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8304,16 +8309,16 @@
         <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>76</v>
@@ -8341,10 +8346,10 @@
         <v>109</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>76</v>
@@ -8362,7 +8367,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8380,7 +8385,7 @@
         <v>76</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>130</v>
@@ -8388,10 +8393,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8414,19 +8419,19 @@
         <v>86</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>76</v>
@@ -8451,13 +8456,13 @@
         <v>76</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>76</v>
@@ -8475,7 +8480,7 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8493,18 +8498,18 @@
         <v>76</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8530,10 +8535,10 @@
         <v>87</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8584,7 +8589,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8593,7 +8598,7 @@
         <v>85</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>76</v>
@@ -8602,7 +8607,7 @@
         <v>76</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>76</v>
@@ -8610,10 +8615,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8639,10 +8644,10 @@
         <v>132</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>148</v>
@@ -8686,7 +8691,7 @@
         <v>135</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>76</v>
@@ -8695,7 +8700,7 @@
         <v>136</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8713,7 +8718,7 @@
         <v>76</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>76</v>
@@ -8721,10 +8726,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8747,19 +8752,19 @@
         <v>86</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>76</v>
@@ -8808,7 +8813,7 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8826,18 +8831,18 @@
         <v>76</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8863,10 +8868,10 @@
         <v>87</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8917,7 +8922,7 @@
         <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8926,7 +8931,7 @@
         <v>85</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>76</v>
@@ -8935,7 +8940,7 @@
         <v>76</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>76</v>
@@ -8943,10 +8948,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8972,10 +8977,10 @@
         <v>132</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>148</v>
@@ -9019,7 +9024,7 @@
         <v>135</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>76</v>
@@ -9028,7 +9033,7 @@
         <v>136</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -9046,7 +9051,7 @@
         <v>76</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>76</v>
@@ -9054,10 +9059,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9083,16 +9088,16 @@
         <v>99</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>76</v>
@@ -9102,7 +9107,7 @@
         <v>76</v>
       </c>
       <c r="S63" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="T63" t="s" s="2">
         <v>76</v>
@@ -9141,7 +9146,7 @@
         <v>76</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -9159,18 +9164,18 @@
         <v>76</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9193,16 +9198,16 @@
         <v>86</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9252,7 +9257,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -9270,18 +9275,18 @@
         <v>76</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9307,14 +9312,14 @@
         <v>105</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>76</v>
@@ -9324,7 +9329,7 @@
         <v>76</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>76</v>
@@ -9363,7 +9368,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -9372,7 +9377,7 @@
         <v>85</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>97</v>
@@ -9381,18 +9386,18 @@
         <v>76</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9415,17 +9420,17 @@
         <v>86</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>76</v>
@@ -9435,7 +9440,7 @@
         <v>76</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>76</v>
@@ -9474,7 +9479,7 @@
         <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9483,7 +9488,7 @@
         <v>85</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>97</v>
@@ -9492,18 +9497,18 @@
         <v>76</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9526,19 +9531,19 @@
         <v>86</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>76</v>
@@ -9587,7 +9592,7 @@
         <v>76</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9605,18 +9610,18 @@
         <v>76</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9639,19 +9644,19 @@
         <v>86</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>76</v>
@@ -9661,7 +9666,7 @@
         <v>76</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>76</v>
@@ -9700,7 +9705,7 @@
         <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9718,18 +9723,18 @@
         <v>76</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9755,29 +9760,29 @@
         <v>99</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>76</v>
       </c>
       <c r="T69" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="U69" t="s" s="2">
         <v>76</v>
@@ -9813,7 +9818,7 @@
         <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9831,18 +9836,18 @@
         <v>76</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9865,16 +9870,16 @@
         <v>86</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9888,7 +9893,7 @@
         <v>76</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>76</v>
@@ -9924,7 +9929,7 @@
         <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9933,7 +9938,7 @@
         <v>85</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>97</v>
@@ -9942,18 +9947,18 @@
         <v>76</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9976,13 +9981,13 @@
         <v>86</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10033,7 +10038,7 @@
         <v>76</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -10051,18 +10056,18 @@
         <v>76</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10085,16 +10090,16 @@
         <v>86</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10144,7 +10149,7 @@
         <v>76</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -10162,18 +10167,18 @@
         <v>76</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10199,10 +10204,10 @@
         <v>153</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10253,7 +10258,7 @@
         <v>76</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -10268,21 +10273,21 @@
         <v>97</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10308,13 +10313,13 @@
         <v>105</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10343,10 +10348,10 @@
         <v>109</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>76</v>
@@ -10364,7 +10369,7 @@
         <v>76</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -10379,21 +10384,21 @@
         <v>97</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10416,16 +10421,16 @@
         <v>86</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10455,7 +10460,7 @@
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>76</v>
@@ -10473,7 +10478,7 @@
         <v>76</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -10488,21 +10493,21 @@
         <v>97</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10528,10 +10533,10 @@
         <v>87</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10582,7 +10587,7 @@
         <v>76</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
@@ -10591,7 +10596,7 @@
         <v>85</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>76</v>
@@ -10600,7 +10605,7 @@
         <v>76</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>76</v>
@@ -10608,10 +10613,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10637,10 +10642,10 @@
         <v>132</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>148</v>
@@ -10684,7 +10689,7 @@
         <v>135</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>76</v>
@@ -10693,7 +10698,7 @@
         <v>136</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
@@ -10711,7 +10716,7 @@
         <v>76</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>76</v>
@@ -10719,10 +10724,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10745,19 +10750,19 @@
         <v>86</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>76</v>
@@ -10806,7 +10811,7 @@
         <v>76</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
@@ -10824,18 +10829,18 @@
         <v>76</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10858,19 +10863,19 @@
         <v>86</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>76</v>
@@ -10880,7 +10885,7 @@
         <v>76</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>76</v>
@@ -10919,7 +10924,7 @@
         <v>76</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>77</v>
@@ -10937,18 +10942,18 @@
         <v>76</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10971,17 +10976,17 @@
         <v>86</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>76</v>
@@ -11030,7 +11035,7 @@
         <v>76</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>77</v>
@@ -11045,10 +11050,10 @@
         <v>97</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>76</v>
@@ -11056,10 +11061,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11082,13 +11087,13 @@
         <v>86</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11139,7 +11144,7 @@
         <v>76</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
@@ -11154,21 +11159,21 @@
         <v>97</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11191,16 +11196,16 @@
         <v>76</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11250,7 +11255,7 @@
         <v>76</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
@@ -11268,7 +11273,7 @@
         <v>76</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>76</v>
@@ -11276,10 +11281,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11302,16 +11307,16 @@
         <v>76</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11361,7 +11366,7 @@
         <v>76</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
@@ -11376,21 +11381,21 @@
         <v>97</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11416,10 +11421,10 @@
         <v>105</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11449,10 +11454,10 @@
         <v>109</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>76</v>
@@ -11470,7 +11475,7 @@
         <v>76</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>77</v>
@@ -11496,10 +11501,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11522,13 +11527,13 @@
         <v>76</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11555,13 +11560,13 @@
         <v>76</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>76</v>
@@ -11579,7 +11584,7 @@
         <v>76</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>77</v>
@@ -11600,15 +11605,15 @@
         <v>76</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11631,13 +11636,13 @@
         <v>76</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11688,7 +11693,7 @@
         <v>76</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>77</v>
@@ -11706,7 +11711,7 @@
         <v>76</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>76</v>
@@ -11714,10 +11719,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11740,13 +11745,13 @@
         <v>76</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11797,7 +11802,7 @@
         <v>76</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>77</v>
@@ -11806,7 +11811,7 @@
         <v>85</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>76</v>
@@ -11815,7 +11820,7 @@
         <v>76</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>76</v>
@@ -11823,10 +11828,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11852,10 +11857,10 @@
         <v>132</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N88" t="s" s="2">
         <v>148</v>
@@ -11908,7 +11913,7 @@
         <v>76</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
@@ -11926,7 +11931,7 @@
         <v>76</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>76</v>
@@ -11934,14 +11939,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -11963,10 +11968,10 @@
         <v>132</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>148</v>
@@ -12021,7 +12026,7 @@
         <v>76</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>
@@ -12047,10 +12052,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12073,13 +12078,13 @@
         <v>76</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12106,13 +12111,13 @@
         <v>76</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>76</v>
@@ -12130,7 +12135,7 @@
         <v>76</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>85</v>
@@ -12145,10 +12150,10 @@
         <v>97</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>76</v>
@@ -12156,10 +12161,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12182,13 +12187,13 @@
         <v>76</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12239,7 +12244,7 @@
         <v>76</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>85</v>
@@ -12257,7 +12262,7 @@
         <v>76</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>76</v>
@@ -12265,10 +12270,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12291,13 +12296,13 @@
         <v>76</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12348,7 +12353,7 @@
         <v>76</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>77</v>
@@ -12366,18 +12371,18 @@
         <v>76</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12400,13 +12405,13 @@
         <v>76</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -12457,7 +12462,7 @@
         <v>76</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>77</v>
@@ -12466,7 +12471,7 @@
         <v>85</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>76</v>
@@ -12475,7 +12480,7 @@
         <v>76</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>76</v>
@@ -12483,10 +12488,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12512,10 +12517,10 @@
         <v>132</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>148</v>
@@ -12568,7 +12573,7 @@
         <v>76</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>77</v>
@@ -12586,7 +12591,7 @@
         <v>76</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>76</v>
@@ -12594,14 +12599,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -12623,10 +12628,10 @@
         <v>132</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>148</v>
@@ -12681,7 +12686,7 @@
         <v>76</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>77</v>
@@ -12707,10 +12712,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12733,13 +12738,13 @@
         <v>86</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -12790,7 +12795,7 @@
         <v>76</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>77</v>
@@ -12805,21 +12810,21 @@
         <v>97</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12842,13 +12847,13 @@
         <v>86</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -12887,7 +12892,7 @@
         <v>76</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AC97" s="2"/>
       <c r="AD97" t="s" s="2">
@@ -12897,7 +12902,7 @@
         <v>136</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>77</v>
@@ -12912,24 +12917,24 @@
         <v>97</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>76</v>
@@ -12951,13 +12956,13 @@
         <v>86</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13008,7 +13013,7 @@
         <v>76</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>77</v>
@@ -13023,21 +13028,21 @@
         <v>97</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13060,13 +13065,13 @@
         <v>86</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13117,7 +13122,7 @@
         <v>76</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>77</v>
@@ -13132,7 +13137,7 @@
         <v>97</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>76</v>
@@ -13143,10 +13148,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13169,13 +13174,13 @@
         <v>76</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13226,7 +13231,7 @@
         <v>76</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>77</v>
@@ -13244,18 +13249,18 @@
         <v>76</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13278,13 +13283,13 @@
         <v>76</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -13311,13 +13316,13 @@
         <v>76</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>76</v>
@@ -13335,7 +13340,7 @@
         <v>76</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>77</v>
@@ -13353,18 +13358,18 @@
         <v>76</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13387,13 +13392,13 @@
         <v>76</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -13420,10 +13425,10 @@
         <v>76</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Z102" t="s" s="2">
         <v>76</v>
@@ -13444,7 +13449,7 @@
         <v>76</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>77</v>
@@ -13462,18 +13467,18 @@
         <v>76</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13496,13 +13501,13 @@
         <v>76</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -13553,7 +13558,7 @@
         <v>76</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>77</v>
@@ -13579,10 +13584,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13605,16 +13610,16 @@
         <v>76</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -13640,13 +13645,13 @@
         <v>76</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>76</v>
@@ -13664,7 +13669,7 @@
         <v>76</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>77</v>
@@ -13682,18 +13687,18 @@
         <v>76</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13716,19 +13721,19 @@
         <v>86</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>76</v>
@@ -13753,13 +13758,13 @@
         <v>76</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>76</v>
@@ -13777,7 +13782,7 @@
         <v>76</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>77</v>
@@ -13798,15 +13803,15 @@
         <v>76</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13829,13 +13834,13 @@
         <v>76</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -13886,7 +13891,7 @@
         <v>76</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>77</v>
@@ -13904,7 +13909,7 @@
         <v>76</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>76</v>
@@ -13912,10 +13917,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13938,13 +13943,13 @@
         <v>76</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -13995,7 +14000,7 @@
         <v>76</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>77</v>
@@ -14004,7 +14009,7 @@
         <v>85</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>76</v>
@@ -14013,7 +14018,7 @@
         <v>76</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>76</v>
@@ -14021,10 +14026,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14050,10 +14055,10 @@
         <v>132</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>148</v>
@@ -14106,7 +14111,7 @@
         <v>76</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>77</v>
@@ -14124,7 +14129,7 @@
         <v>76</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>76</v>
@@ -14132,14 +14137,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -14161,10 +14166,10 @@
         <v>132</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>148</v>
@@ -14219,7 +14224,7 @@
         <v>76</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>77</v>
@@ -14245,10 +14250,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14271,13 +14276,13 @@
         <v>76</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -14328,7 +14333,7 @@
         <v>76</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>77</v>
@@ -14346,7 +14351,7 @@
         <v>76</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>76</v>
@@ -14354,10 +14359,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14380,13 +14385,13 @@
         <v>76</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -14413,13 +14418,13 @@
         <v>76</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>76</v>
@@ -14437,7 +14442,7 @@
         <v>76</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>77</v>
@@ -14455,7 +14460,7 @@
         <v>76</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>76</v>
@@ -14463,10 +14468,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14489,13 +14494,13 @@
         <v>76</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -14546,7 +14551,7 @@
         <v>76</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>77</v>
@@ -14564,18 +14569,18 @@
         <v>76</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14598,13 +14603,13 @@
         <v>76</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -14643,17 +14648,17 @@
         <v>76</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AC113" s="2"/>
       <c r="AD113" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>77</v>
@@ -14671,7 +14676,7 @@
         <v>76</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>76</v>
@@ -14679,13 +14684,13 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>76</v>
@@ -14707,13 +14712,13 @@
         <v>76</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -14764,7 +14769,7 @@
         <v>76</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>77</v>
@@ -14782,7 +14787,7 @@
         <v>76</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>76</v>
@@ -14790,10 +14795,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14816,13 +14821,13 @@
         <v>76</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -14873,7 +14878,7 @@
         <v>76</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>77</v>
@@ -14891,7 +14896,7 @@
         <v>76</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>76</v>
@@ -14899,10 +14904,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14925,13 +14930,13 @@
         <v>76</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -14982,7 +14987,7 @@
         <v>76</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>77</v>
@@ -14991,7 +14996,7 @@
         <v>85</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>76</v>
@@ -15000,7 +15005,7 @@
         <v>76</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>76</v>
@@ -15008,10 +15013,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15037,10 +15042,10 @@
         <v>132</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>148</v>
@@ -15093,7 +15098,7 @@
         <v>76</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>77</v>
@@ -15111,7 +15116,7 @@
         <v>76</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>76</v>
@@ -15119,14 +15124,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -15148,10 +15153,10 @@
         <v>132</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>148</v>
@@ -15206,7 +15211,7 @@
         <v>76</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>77</v>
@@ -15232,10 +15237,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15258,13 +15263,13 @@
         <v>76</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -15315,7 +15320,7 @@
         <v>76</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>85</v>
@@ -15333,7 +15338,7 @@
         <v>76</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>76</v>
@@ -15341,10 +15346,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15367,13 +15372,13 @@
         <v>76</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -15424,7 +15429,7 @@
         <v>76</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>77</v>
@@ -15439,10 +15444,10 @@
         <v>97</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>76</v>
@@ -15450,10 +15455,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15476,13 +15481,13 @@
         <v>76</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -15533,7 +15538,7 @@
         <v>76</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>77</v>
@@ -15551,18 +15556,18 @@
         <v>76</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15585,19 +15590,19 @@
         <v>86</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>76</v>
@@ -15622,13 +15627,13 @@
         <v>76</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>76</v>
@@ -15646,7 +15651,7 @@
         <v>76</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>77</v>
@@ -15667,15 +15672,15 @@
         <v>76</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -15698,13 +15703,13 @@
         <v>76</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L123" t="s" s="2">
         <v>50</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -15755,7 +15760,7 @@
         <v>76</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>77</v>
@@ -15773,10 +15778,10 @@
         <v>76</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
   </sheetData>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:25+00:00</t>
+    <t>2023-05-11T10:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:56+00:00</t>
+    <t>2023-05-11T10:34:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:34:10+00:00</t>
+    <t>2023-05-11T10:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4328" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4328" uniqueCount="576">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:41:58+00:00</t>
+    <t>2023-05-11T10:56:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -510,9 +510,6 @@
   </si>
   <si>
     <t>Slice based on the type of identifier.</t>
-  </si>
-  <si>
-    <t>openAtEnd</t>
   </si>
   <si>
     <t>FiveWs.identifier</t>
@@ -3468,7 +3465,7 @@
         <v>76</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="AF12" t="s" s="2">
         <v>151</v>
@@ -3486,24 +3483,24 @@
         <v>97</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AM12" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>161</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>151</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>76</v>
@@ -3597,21 +3594,21 @@
         <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>161</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3637,10 +3634,10 @@
         <v>87</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3691,25 +3688,25 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI14" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AG14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI14" t="s" s="2">
+      <c r="AJ14" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>76</v>
@@ -3717,10 +3714,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3746,10 +3743,10 @@
         <v>132</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N15" t="s" s="2">
         <v>148</v>
@@ -3793,7 +3790,7 @@
         <v>135</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>76</v>
@@ -3802,7 +3799,7 @@
         <v>136</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3820,7 +3817,7 @@
         <v>76</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>76</v>
@@ -3828,10 +3825,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3857,16 +3854,16 @@
         <v>105</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>76</v>
@@ -3894,28 +3891,28 @@
         <v>109</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3933,7 +3930,7 @@
         <v>76</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>130</v>
@@ -3941,10 +3938,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3967,19 +3964,19 @@
         <v>86</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>76</v>
@@ -4004,31 +4001,31 @@
         <v>76</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Y17" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="Z17" t="s" s="2">
+      <c r="AA17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -4046,18 +4043,18 @@
         <v>76</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4083,10 +4080,10 @@
         <v>87</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4137,25 +4134,25 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI18" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AG18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI18" t="s" s="2">
+      <c r="AJ18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>76</v>
@@ -4163,10 +4160,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4192,10 +4189,10 @@
         <v>132</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>148</v>
@@ -4239,7 +4236,7 @@
         <v>135</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>76</v>
@@ -4248,7 +4245,7 @@
         <v>136</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -4266,7 +4263,7 @@
         <v>76</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>76</v>
@@ -4274,10 +4271,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4300,19 +4297,19 @@
         <v>86</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -4361,7 +4358,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -4379,18 +4376,18 @@
         <v>76</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>212</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4416,10 +4413,10 @@
         <v>87</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4470,25 +4467,25 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI21" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AG21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI21" t="s" s="2">
+      <c r="AJ21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>76</v>
@@ -4496,10 +4493,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4525,10 +4522,10 @@
         <v>132</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>148</v>
@@ -4572,7 +4569,7 @@
         <v>135</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>76</v>
@@ -4581,7 +4578,7 @@
         <v>136</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4599,7 +4596,7 @@
         <v>76</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>76</v>
@@ -4607,10 +4604,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4636,16 +4633,16 @@
         <v>99</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>76</v>
@@ -4655,46 +4652,46 @@
         <v>76</v>
       </c>
       <c r="S23" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="T23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4712,18 +4709,18 @@
         <v>76</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>226</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4746,16 +4743,16 @@
         <v>86</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4805,7 +4802,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4823,18 +4820,18 @@
         <v>76</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>235</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4860,14 +4857,14 @@
         <v>105</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4877,55 +4874,55 @@
         <v>76</v>
       </c>
       <c r="S25" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="T25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF25" t="s" s="2">
+      <c r="AG25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI25" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>97</v>
@@ -4934,18 +4931,18 @@
         <v>76</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>245</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4968,17 +4965,17 @@
         <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>76</v>
@@ -4988,47 +4985,47 @@
         <v>76</v>
       </c>
       <c r="S26" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="T26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>252</v>
-      </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
@@ -5036,7 +5033,7 @@
         <v>85</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>97</v>
@@ -5045,18 +5042,18 @@
         <v>76</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>254</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5079,19 +5076,19 @@
         <v>86</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -5140,7 +5137,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -5158,18 +5155,18 @@
         <v>76</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>264</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5192,19 +5189,19 @@
         <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>76</v>
@@ -5214,46 +5211,46 @@
         <v>76</v>
       </c>
       <c r="S28" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="T28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -5271,18 +5268,18 @@
         <v>76</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>274</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5308,65 +5305,65 @@
         <v>99</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T29" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="S29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T29" t="s" s="2">
+      <c r="U29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -5384,18 +5381,18 @@
         <v>76</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>285</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5418,16 +5415,16 @@
         <v>86</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5441,52 +5438,52 @@
         <v>76</v>
       </c>
       <c r="T30" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="U30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF30" t="s" s="2">
+      <c r="AG30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI30" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>97</v>
@@ -5495,18 +5492,18 @@
         <v>76</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>295</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5529,13 +5526,13 @@
         <v>86</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5586,7 +5583,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5604,18 +5601,18 @@
         <v>76</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>303</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5638,16 +5635,16 @@
         <v>86</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5697,7 +5694,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5715,21 +5712,21 @@
         <v>76</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>312</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>151</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>76</v>
@@ -5823,21 +5820,21 @@
         <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>161</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5863,10 +5860,10 @@
         <v>87</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5917,25 +5914,25 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI34" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AG34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI34" t="s" s="2">
+      <c r="AJ34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>76</v>
@@ -5943,10 +5940,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5972,10 +5969,10 @@
         <v>132</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>148</v>
@@ -6019,7 +6016,7 @@
         <v>135</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>76</v>
@@ -6028,7 +6025,7 @@
         <v>136</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -6046,7 +6043,7 @@
         <v>76</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>76</v>
@@ -6054,10 +6051,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6083,16 +6080,16 @@
         <v>105</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>76</v>
@@ -6120,28 +6117,28 @@
         <v>109</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Z36" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Z36" t="s" s="2">
+      <c r="AA36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -6159,7 +6156,7 @@
         <v>76</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>130</v>
@@ -6167,10 +6164,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6193,19 +6190,19 @@
         <v>86</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>76</v>
@@ -6230,31 +6227,31 @@
         <v>76</v>
       </c>
       <c r="X37" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Y37" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="Y37" t="s" s="2">
+      <c r="Z37" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="Z37" t="s" s="2">
+      <c r="AA37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -6272,18 +6269,18 @@
         <v>76</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6309,10 +6306,10 @@
         <v>87</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6363,25 +6360,25 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI38" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AG38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI38" t="s" s="2">
+      <c r="AJ38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>76</v>
@@ -6389,10 +6386,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6418,10 +6415,10 @@
         <v>132</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>148</v>
@@ -6465,7 +6462,7 @@
         <v>135</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>76</v>
@@ -6474,7 +6471,7 @@
         <v>136</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6492,7 +6489,7 @@
         <v>76</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>76</v>
@@ -6500,10 +6497,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6526,19 +6523,19 @@
         <v>86</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>76</v>
@@ -6587,7 +6584,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6605,18 +6602,18 @@
         <v>76</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>212</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6642,10 +6639,10 @@
         <v>87</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6696,25 +6693,25 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI41" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AG41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI41" t="s" s="2">
+      <c r="AJ41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>76</v>
@@ -6722,10 +6719,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6751,10 +6748,10 @@
         <v>132</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>148</v>
@@ -6798,7 +6795,7 @@
         <v>135</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>76</v>
@@ -6807,7 +6804,7 @@
         <v>136</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6825,7 +6822,7 @@
         <v>76</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>76</v>
@@ -6833,10 +6830,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6862,16 +6859,16 @@
         <v>99</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>76</v>
@@ -6881,46 +6878,46 @@
         <v>76</v>
       </c>
       <c r="S43" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6938,18 +6935,18 @@
         <v>76</v>
       </c>
       <c r="AL43" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>226</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6972,16 +6969,16 @@
         <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7031,7 +7028,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -7049,18 +7046,18 @@
         <v>76</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>235</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7086,14 +7083,14 @@
         <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>76</v>
@@ -7103,55 +7100,55 @@
         <v>76</v>
       </c>
       <c r="S45" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="T45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF45" t="s" s="2">
+      <c r="AG45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI45" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>97</v>
@@ -7160,18 +7157,18 @@
         <v>76</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>245</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7194,17 +7191,17 @@
         <v>86</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -7214,47 +7211,47 @@
         <v>76</v>
       </c>
       <c r="S46" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF46" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="T46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>252</v>
-      </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
       </c>
@@ -7262,7 +7259,7 @@
         <v>85</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>97</v>
@@ -7271,18 +7268,18 @@
         <v>76</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>254</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7305,19 +7302,19 @@
         <v>86</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>76</v>
@@ -7366,7 +7363,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -7384,18 +7381,18 @@
         <v>76</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>264</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7418,19 +7415,19 @@
         <v>86</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>76</v>
@@ -7440,7 +7437,7 @@
         <v>76</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="T48" t="s" s="2">
         <v>76</v>
@@ -7479,7 +7476,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7497,18 +7494,18 @@
         <v>76</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>274</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7534,65 +7531,65 @@
         <v>99</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="T49" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7610,18 +7607,18 @@
         <v>76</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>285</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7644,16 +7641,16 @@
         <v>86</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7667,52 +7664,52 @@
         <v>76</v>
       </c>
       <c r="T50" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="U50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF50" t="s" s="2">
+      <c r="AG50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI50" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>97</v>
@@ -7721,18 +7718,18 @@
         <v>76</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>295</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7755,13 +7752,13 @@
         <v>86</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7812,7 +7809,7 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7830,18 +7827,18 @@
         <v>76</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>303</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7864,16 +7861,16 @@
         <v>86</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7923,7 +7920,7 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7941,21 +7938,21 @@
         <v>76</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>312</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>151</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>76</v>
@@ -8049,21 +8046,21 @@
         <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AL53" t="s" s="2">
+      <c r="AM53" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>161</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8089,10 +8086,10 @@
         <v>87</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8143,25 +8140,25 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI54" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AG54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI54" t="s" s="2">
+      <c r="AJ54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>76</v>
@@ -8169,10 +8166,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8198,10 +8195,10 @@
         <v>132</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>148</v>
@@ -8245,7 +8242,7 @@
         <v>135</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>76</v>
@@ -8254,7 +8251,7 @@
         <v>136</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -8272,7 +8269,7 @@
         <v>76</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>76</v>
@@ -8280,10 +8277,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8309,16 +8306,16 @@
         <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>76</v>
@@ -8346,28 +8343,28 @@
         <v>109</v>
       </c>
       <c r="Y56" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Z56" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Z56" t="s" s="2">
+      <c r="AA56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8385,7 +8382,7 @@
         <v>76</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>130</v>
@@ -8393,10 +8390,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8419,19 +8416,19 @@
         <v>86</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>76</v>
@@ -8456,31 +8453,31 @@
         <v>76</v>
       </c>
       <c r="X57" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Y57" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="Y57" t="s" s="2">
+      <c r="Z57" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="Z57" t="s" s="2">
+      <c r="AA57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8498,18 +8495,18 @@
         <v>76</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8535,10 +8532,10 @@
         <v>87</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8589,25 +8586,25 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI58" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AG58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI58" t="s" s="2">
+      <c r="AJ58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>76</v>
@@ -8615,10 +8612,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8644,10 +8641,10 @@
         <v>132</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>148</v>
@@ -8691,7 +8688,7 @@
         <v>135</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>76</v>
@@ -8700,7 +8697,7 @@
         <v>136</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8718,7 +8715,7 @@
         <v>76</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>76</v>
@@ -8726,10 +8723,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8752,19 +8749,19 @@
         <v>86</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>76</v>
@@ -8813,7 +8810,7 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8831,18 +8828,18 @@
         <v>76</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>212</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8868,10 +8865,10 @@
         <v>87</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8922,25 +8919,25 @@
         <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI61" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AG61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI61" t="s" s="2">
+      <c r="AJ61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>76</v>
@@ -8948,10 +8945,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8977,10 +8974,10 @@
         <v>132</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>148</v>
@@ -9024,7 +9021,7 @@
         <v>135</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>76</v>
@@ -9033,7 +9030,7 @@
         <v>136</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -9051,7 +9048,7 @@
         <v>76</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>76</v>
@@ -9059,10 +9056,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9088,16 +9085,16 @@
         <v>99</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>76</v>
@@ -9107,46 +9104,46 @@
         <v>76</v>
       </c>
       <c r="S63" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF63" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -9164,18 +9161,18 @@
         <v>76</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>226</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9198,16 +9195,16 @@
         <v>86</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9257,7 +9254,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -9275,18 +9272,18 @@
         <v>76</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>235</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9312,14 +9309,14 @@
         <v>105</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>76</v>
@@ -9329,55 +9326,55 @@
         <v>76</v>
       </c>
       <c r="S65" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="T65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF65" t="s" s="2">
+      <c r="AG65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI65" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>97</v>
@@ -9386,18 +9383,18 @@
         <v>76</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>245</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9420,17 +9417,17 @@
         <v>86</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>76</v>
@@ -9440,47 +9437,47 @@
         <v>76</v>
       </c>
       <c r="S66" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="T66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>252</v>
-      </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9488,7 +9485,7 @@
         <v>85</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>97</v>
@@ -9497,18 +9494,18 @@
         <v>76</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>254</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9531,19 +9528,19 @@
         <v>86</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>76</v>
@@ -9592,7 +9589,7 @@
         <v>76</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9610,18 +9607,18 @@
         <v>76</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>264</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9644,19 +9641,19 @@
         <v>86</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>76</v>
@@ -9666,7 +9663,7 @@
         <v>76</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>76</v>
@@ -9705,7 +9702,7 @@
         <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9723,18 +9720,18 @@
         <v>76</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>274</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9760,65 +9757,65 @@
         <v>99</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>76</v>
       </c>
       <c r="T69" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9836,18 +9833,18 @@
         <v>76</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>285</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9870,16 +9867,16 @@
         <v>86</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9893,52 +9890,52 @@
         <v>76</v>
       </c>
       <c r="T70" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="U70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF70" t="s" s="2">
+      <c r="AG70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI70" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>97</v>
@@ -9947,18 +9944,18 @@
         <v>76</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>295</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9981,13 +9978,13 @@
         <v>86</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10038,7 +10035,7 @@
         <v>76</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -10056,18 +10053,18 @@
         <v>76</v>
       </c>
       <c r="AL71" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>303</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10090,16 +10087,16 @@
         <v>86</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10149,7 +10146,7 @@
         <v>76</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -10167,18 +10164,18 @@
         <v>76</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>312</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10204,10 +10201,10 @@
         <v>153</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10258,7 +10255,7 @@
         <v>76</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -10273,21 +10270,21 @@
         <v>97</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AL73" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>363</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10313,13 +10310,13 @@
         <v>105</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10348,11 +10345,11 @@
         <v>109</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="Z74" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="Z74" t="s" s="2">
-        <v>369</v>
-      </c>
       <c r="AA74" t="s" s="2">
         <v>76</v>
       </c>
@@ -10369,7 +10366,7 @@
         <v>76</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -10384,21 +10381,21 @@
         <v>97</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AL74" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AL74" t="s" s="2">
+      <c r="AM74" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>372</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10421,16 +10418,16 @@
         <v>86</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10460,7 +10457,7 @@
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>76</v>
@@ -10478,7 +10475,7 @@
         <v>76</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -10493,21 +10490,21 @@
         <v>97</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AL75" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AL75" t="s" s="2">
+      <c r="AM75" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>380</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10533,10 +10530,10 @@
         <v>87</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10587,25 +10584,25 @@
         <v>76</v>
       </c>
       <c r="AF76" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI76" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AG76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI76" t="s" s="2">
+      <c r="AJ76" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL76" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>76</v>
@@ -10613,10 +10610,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10642,10 +10639,10 @@
         <v>132</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>148</v>
@@ -10689,7 +10686,7 @@
         <v>135</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>76</v>
@@ -10698,7 +10695,7 @@
         <v>136</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
@@ -10716,7 +10713,7 @@
         <v>76</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>76</v>
@@ -10724,10 +10721,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10750,19 +10747,19 @@
         <v>86</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>76</v>
@@ -10811,7 +10808,7 @@
         <v>76</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
@@ -10829,18 +10826,18 @@
         <v>76</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AM78" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>212</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10863,19 +10860,19 @@
         <v>86</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="N79" t="s" s="2">
+      <c r="O79" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>76</v>
@@ -10885,7 +10882,7 @@
         <v>76</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>76</v>
@@ -10924,7 +10921,7 @@
         <v>76</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>77</v>
@@ -10942,18 +10939,18 @@
         <v>76</v>
       </c>
       <c r="AL79" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AM79" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>274</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10976,17 +10973,17 @@
         <v>86</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>76</v>
@@ -11035,7 +11032,7 @@
         <v>76</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>77</v>
@@ -11050,10 +11047,10 @@
         <v>97</v>
       </c>
       <c r="AK80" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AL80" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>76</v>
@@ -11061,10 +11058,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11087,13 +11084,13 @@
         <v>86</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11144,7 +11141,7 @@
         <v>76</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
@@ -11159,21 +11156,21 @@
         <v>97</v>
       </c>
       <c r="AK81" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AL81" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AL81" t="s" s="2">
+      <c r="AM81" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>399</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11196,16 +11193,16 @@
         <v>76</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11255,7 +11252,7 @@
         <v>76</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
@@ -11273,7 +11270,7 @@
         <v>76</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>76</v>
@@ -11281,10 +11278,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11307,16 +11304,16 @@
         <v>76</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11366,7 +11363,7 @@
         <v>76</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
@@ -11381,21 +11378,21 @@
         <v>97</v>
       </c>
       <c r="AK83" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AL83" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AL83" t="s" s="2">
+      <c r="AM83" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>413</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11421,10 +11418,10 @@
         <v>105</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11454,11 +11451,11 @@
         <v>109</v>
       </c>
       <c r="Y84" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="Z84" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="Z84" t="s" s="2">
-        <v>418</v>
-      </c>
       <c r="AA84" t="s" s="2">
         <v>76</v>
       </c>
@@ -11475,7 +11472,7 @@
         <v>76</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>77</v>
@@ -11501,10 +11498,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11527,13 +11524,13 @@
         <v>76</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11560,14 +11557,14 @@
         <v>76</v>
       </c>
       <c r="X85" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="Y85" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="Y85" t="s" s="2">
+      <c r="Z85" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="Z85" t="s" s="2">
-        <v>424</v>
-      </c>
       <c r="AA85" t="s" s="2">
         <v>76</v>
       </c>
@@ -11584,7 +11581,7 @@
         <v>76</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>77</v>
@@ -11605,15 +11602,15 @@
         <v>76</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11636,13 +11633,13 @@
         <v>76</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11693,7 +11690,7 @@
         <v>76</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>77</v>
@@ -11711,7 +11708,7 @@
         <v>76</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>76</v>
@@ -11719,10 +11716,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11745,13 +11742,13 @@
         <v>76</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11802,25 +11799,25 @@
         <v>76</v>
       </c>
       <c r="AF87" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI87" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AG87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI87" t="s" s="2">
+      <c r="AJ87" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL87" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>76</v>
@@ -11828,10 +11825,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11857,10 +11854,10 @@
         <v>132</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N88" t="s" s="2">
         <v>148</v>
@@ -11913,7 +11910,7 @@
         <v>76</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
@@ -11931,7 +11928,7 @@
         <v>76</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>76</v>
@@ -11939,14 +11936,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -11968,10 +11965,10 @@
         <v>132</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>148</v>
@@ -12026,7 +12023,7 @@
         <v>76</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>
@@ -12052,10 +12049,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12078,13 +12075,13 @@
         <v>76</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12111,14 +12108,14 @@
         <v>76</v>
       </c>
       <c r="X90" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="Y90" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="Y90" t="s" s="2">
+      <c r="Z90" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="Z90" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="AA90" t="s" s="2">
         <v>76</v>
       </c>
@@ -12135,7 +12132,7 @@
         <v>76</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>85</v>
@@ -12150,10 +12147,10 @@
         <v>97</v>
       </c>
       <c r="AK90" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AL90" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>76</v>
@@ -12161,10 +12158,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12187,13 +12184,13 @@
         <v>76</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12244,7 +12241,7 @@
         <v>76</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>85</v>
@@ -12262,7 +12259,7 @@
         <v>76</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>76</v>
@@ -12270,10 +12267,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12296,13 +12293,13 @@
         <v>76</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12353,7 +12350,7 @@
         <v>76</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>77</v>
@@ -12371,18 +12368,18 @@
         <v>76</v>
       </c>
       <c r="AL92" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AM92" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>452</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12405,13 +12402,13 @@
         <v>76</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -12462,25 +12459,25 @@
         <v>76</v>
       </c>
       <c r="AF93" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI93" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AG93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI93" t="s" s="2">
+      <c r="AJ93" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL93" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>76</v>
@@ -12488,10 +12485,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12517,10 +12514,10 @@
         <v>132</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>148</v>
@@ -12573,7 +12570,7 @@
         <v>76</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>77</v>
@@ -12591,7 +12588,7 @@
         <v>76</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>76</v>
@@ -12599,14 +12596,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -12628,10 +12625,10 @@
         <v>132</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>148</v>
@@ -12686,7 +12683,7 @@
         <v>76</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>77</v>
@@ -12712,10 +12709,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12738,13 +12735,13 @@
         <v>86</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -12795,7 +12792,7 @@
         <v>76</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>77</v>
@@ -12810,21 +12807,21 @@
         <v>97</v>
       </c>
       <c r="AK96" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AL96" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AL96" t="s" s="2">
+      <c r="AM96" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>462</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12847,13 +12844,13 @@
         <v>86</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -12892,7 +12889,7 @@
         <v>76</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AC97" s="2"/>
       <c r="AD97" t="s" s="2">
@@ -12902,7 +12899,7 @@
         <v>136</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>77</v>
@@ -12917,24 +12914,24 @@
         <v>97</v>
       </c>
       <c r="AK97" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AL97" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AL97" t="s" s="2">
+      <c r="AM97" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>470</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C98" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="C98" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>76</v>
@@ -12956,13 +12953,13 @@
         <v>86</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13013,7 +13010,7 @@
         <v>76</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>77</v>
@@ -13028,21 +13025,21 @@
         <v>97</v>
       </c>
       <c r="AK98" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AL98" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AL98" t="s" s="2">
+      <c r="AM98" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>470</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13065,13 +13062,13 @@
         <v>86</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="M99" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13122,7 +13119,7 @@
         <v>76</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>77</v>
@@ -13137,7 +13134,7 @@
         <v>97</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>76</v>
@@ -13148,10 +13145,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13174,13 +13171,13 @@
         <v>76</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="L100" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="L100" t="s" s="2">
+      <c r="M100" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13231,7 +13228,7 @@
         <v>76</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>77</v>
@@ -13249,18 +13246,18 @@
         <v>76</v>
       </c>
       <c r="AL100" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AM100" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>482</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13283,13 +13280,13 @@
         <v>76</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -13316,14 +13313,14 @@
         <v>76</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Y101" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="Z101" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="Z101" t="s" s="2">
-        <v>487</v>
-      </c>
       <c r="AA101" t="s" s="2">
         <v>76</v>
       </c>
@@ -13340,7 +13337,7 @@
         <v>76</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>77</v>
@@ -13358,18 +13355,18 @@
         <v>76</v>
       </c>
       <c r="AL101" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AM101" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>489</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13392,13 +13389,13 @@
         <v>76</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="L102" t="s" s="2">
-        <v>492</v>
-      </c>
       <c r="M102" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -13425,10 +13422,10 @@
         <v>76</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="Z102" t="s" s="2">
         <v>76</v>
@@ -13449,7 +13446,7 @@
         <v>76</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>77</v>
@@ -13467,18 +13464,18 @@
         <v>76</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13501,13 +13498,13 @@
         <v>76</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -13558,7 +13555,7 @@
         <v>76</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>77</v>
@@ -13584,10 +13581,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13610,16 +13607,16 @@
         <v>76</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="L104" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="L104" t="s" s="2">
+      <c r="M104" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -13645,14 +13642,14 @@
         <v>76</v>
       </c>
       <c r="X104" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="Y104" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="Y104" t="s" s="2">
+      <c r="Z104" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="Z104" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="AA104" t="s" s="2">
         <v>76</v>
       </c>
@@ -13669,7 +13666,7 @@
         <v>76</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>77</v>
@@ -13687,18 +13684,18 @@
         <v>76</v>
       </c>
       <c r="AL104" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AM104" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>505</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13721,19 +13718,19 @@
         <v>86</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L105" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="L105" t="s" s="2">
+      <c r="M105" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="N105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>76</v>
@@ -13758,14 +13755,14 @@
         <v>76</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Y105" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="Z105" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="Z105" t="s" s="2">
-        <v>513</v>
-      </c>
       <c r="AA105" t="s" s="2">
         <v>76</v>
       </c>
@@ -13782,7 +13779,7 @@
         <v>76</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>77</v>
@@ -13803,15 +13800,15 @@
         <v>76</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13834,13 +13831,13 @@
         <v>76</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -13891,7 +13888,7 @@
         <v>76</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>77</v>
@@ -13909,7 +13906,7 @@
         <v>76</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>76</v>
@@ -13917,10 +13914,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13943,13 +13940,13 @@
         <v>76</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14000,25 +13997,25 @@
         <v>76</v>
       </c>
       <c r="AF107" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI107" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AG107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI107" t="s" s="2">
+      <c r="AJ107" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL107" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>76</v>
@@ -14026,10 +14023,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14055,10 +14052,10 @@
         <v>132</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>148</v>
@@ -14111,7 +14108,7 @@
         <v>76</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>77</v>
@@ -14129,7 +14126,7 @@
         <v>76</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>76</v>
@@ -14137,14 +14134,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -14166,10 +14163,10 @@
         <v>132</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>148</v>
@@ -14224,7 +14221,7 @@
         <v>76</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>77</v>
@@ -14250,10 +14247,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14276,13 +14273,13 @@
         <v>76</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -14333,7 +14330,7 @@
         <v>76</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>77</v>
@@ -14351,7 +14348,7 @@
         <v>76</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>76</v>
@@ -14359,10 +14356,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14385,13 +14382,13 @@
         <v>76</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -14418,14 +14415,14 @@
         <v>76</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Y111" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="Z111" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="Z111" t="s" s="2">
-        <v>529</v>
-      </c>
       <c r="AA111" t="s" s="2">
         <v>76</v>
       </c>
@@ -14442,7 +14439,7 @@
         <v>76</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>77</v>
@@ -14460,7 +14457,7 @@
         <v>76</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>76</v>
@@ -14468,10 +14465,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14494,13 +14491,13 @@
         <v>76</v>
       </c>
       <c r="K112" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="L112" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="L112" t="s" s="2">
+      <c r="M112" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -14551,7 +14548,7 @@
         <v>76</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>77</v>
@@ -14569,18 +14566,18 @@
         <v>76</v>
       </c>
       <c r="AL112" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AM112" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>535</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14603,13 +14600,13 @@
         <v>76</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -14648,17 +14645,17 @@
         <v>76</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AC113" s="2"/>
       <c r="AD113" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>77</v>
@@ -14676,7 +14673,7 @@
         <v>76</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>76</v>
@@ -14684,13 +14681,13 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="C114" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="C114" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>76</v>
@@ -14712,13 +14709,13 @@
         <v>76</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -14769,7 +14766,7 @@
         <v>76</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>77</v>
@@ -14787,7 +14784,7 @@
         <v>76</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>76</v>
@@ -14795,10 +14792,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14821,13 +14818,13 @@
         <v>76</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -14878,7 +14875,7 @@
         <v>76</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>77</v>
@@ -14896,7 +14893,7 @@
         <v>76</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>76</v>
@@ -14904,10 +14901,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14930,13 +14927,13 @@
         <v>76</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -14987,25 +14984,25 @@
         <v>76</v>
       </c>
       <c r="AF116" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI116" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AG116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI116" t="s" s="2">
+      <c r="AJ116" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL116" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>76</v>
@@ -15013,10 +15010,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15042,10 +15039,10 @@
         <v>132</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>148</v>
@@ -15098,7 +15095,7 @@
         <v>76</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>77</v>
@@ -15116,7 +15113,7 @@
         <v>76</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>76</v>
@@ -15124,14 +15121,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -15153,10 +15150,10 @@
         <v>132</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>148</v>
@@ -15211,7 +15208,7 @@
         <v>76</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>77</v>
@@ -15237,10 +15234,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15263,13 +15260,13 @@
         <v>76</v>
       </c>
       <c r="K119" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="L119" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="L119" t="s" s="2">
+      <c r="M119" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -15320,7 +15317,7 @@
         <v>76</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>85</v>
@@ -15338,7 +15335,7 @@
         <v>76</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>76</v>
@@ -15346,10 +15343,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15372,13 +15369,13 @@
         <v>76</v>
       </c>
       <c r="K120" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="L120" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="L120" t="s" s="2">
+      <c r="M120" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -15429,7 +15426,7 @@
         <v>76</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>77</v>
@@ -15444,10 +15441,10 @@
         <v>97</v>
       </c>
       <c r="AK120" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AL120" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>76</v>
@@ -15455,10 +15452,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15481,13 +15478,13 @@
         <v>76</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -15538,7 +15535,7 @@
         <v>76</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>77</v>
@@ -15556,18 +15553,18 @@
         <v>76</v>
       </c>
       <c r="AL121" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AM121" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>563</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15590,19 +15587,19 @@
         <v>86</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="N122" t="s" s="2">
+      <c r="O122" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>76</v>
@@ -15627,14 +15624,14 @@
         <v>76</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Y122" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="Z122" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="Z122" t="s" s="2">
-        <v>570</v>
-      </c>
       <c r="AA122" t="s" s="2">
         <v>76</v>
       </c>
@@ -15651,7 +15648,7 @@
         <v>76</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>77</v>
@@ -15672,15 +15669,15 @@
         <v>76</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -15703,13 +15700,13 @@
         <v>76</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L123" t="s" s="2">
         <v>50</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -15760,7 +15757,7 @@
         <v>76</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>77</v>
@@ -15778,10 +15775,10 @@
         <v>76</v>
       </c>
       <c r="AL123" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AM123" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>576</v>
       </c>
     </row>
   </sheetData>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:16+00:00</t>
+    <t>2023-05-11T10:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:44+00:00</t>
+    <t>2023-05-11T11:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:14:34+00:00</t>
+    <t>2023-05-11T11:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/viral-load-specimen</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/viral-load-specimen</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:21:30+00:00</t>
+    <t>2023-05-11T11:55:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -456,7 +456,7 @@
     <t>SampleReordered</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/sample-reordered}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/sample-reordered}
 </t>
   </si>
   <si>
@@ -1175,7 +1175,7 @@
     <t>The type can change the way that a specimen is handled and drives what kind of analyses can properly be performed on the specimen. It is frequently used in diagnostic work flow decision making systems.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-specimen-type</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/ValueSet/vs-specimen-type</t>
   </si>
   <si>
     <t>FiveWs.what[x]</t>
@@ -2130,7 +2130,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.2265625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="126.5078125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2145,7 +2145,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="115.21875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="57.9296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="105.2109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:55:17+00:00</t>
+    <t>2023-05-11T12:03:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/viral-load-specimen</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/viral-load-specimen</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:03:20+00:00</t>
+    <t>2023-05-11T12:08:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -456,7 +456,7 @@
     <t>SampleReordered</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/sample-reordered}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/sample-reordered}
 </t>
   </si>
   <si>
@@ -1175,7 +1175,7 @@
     <t>The type can change the way that a specimen is handled and drives what kind of analyses can properly be performed on the specimen. It is frequently used in diagnostic work flow decision making systems.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/ValueSet/vs-specimen-type</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-specimen-type</t>
   </si>
   <si>
     <t>FiveWs.what[x]</t>
@@ -2130,7 +2130,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="126.5078125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="79.2265625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2145,7 +2145,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="115.21875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="105.2109375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="57.9296875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:08:48+00:00</t>
+    <t>2023-05-11T12:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:16:35+00:00</t>
+    <t>2023-05-11T12:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:20:22+00:00</t>
+    <t>2023-05-11T12:21:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:21:18+00:00</t>
+    <t>2023-05-11T15:25:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T15:25:42+00:00</t>
+    <t>2023-05-11T15:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T15:26:02+00:00</t>
+    <t>2023-05-11T16:43:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:02+00:00</t>
+    <t>2023-05-11T16:43:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:55+00:00</t>
+    <t>2023-05-11T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:57:46+00:00</t>
+    <t>2023-05-11T16:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:58:30+00:00</t>
+    <t>2023-05-11T17:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:02+00:00</t>
+    <t>2023-05-11T17:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/viral-load-specimen</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/viral-load-specimen</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:30+00:00</t>
+    <t>2023-05-11T18:15:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -456,7 +456,7 @@
     <t>SampleReordered</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/sample-reordered}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/sample-reordered}
 </t>
   </si>
   <si>
@@ -1175,7 +1175,7 @@
     <t>The type can change the way that a specimen is handled and drives what kind of analyses can properly be performed on the specimen. It is frequently used in diagnostic work flow decision making systems.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-specimen-type</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/ValueSet/vs-specimen-type</t>
   </si>
   <si>
     <t>FiveWs.what[x]</t>
@@ -2130,7 +2130,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.2265625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="122.17578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2145,7 +2145,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="115.21875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="57.9296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="100.87890625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:15:51+00:00</t>
+    <t>2023-05-11T18:16:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/viral-load-specimen</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/viral-load-specimen</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:16:31+00:00</t>
+    <t>2023-05-11T18:27:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -456,7 +456,7 @@
     <t>SampleReordered</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/sample-reordered}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/sample-reordered}
 </t>
   </si>
   <si>
@@ -1175,7 +1175,7 @@
     <t>The type can change the way that a specimen is handled and drives what kind of analyses can properly be performed on the specimen. It is frequently used in diagnostic work flow decision making systems.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/ValueSet/vs-specimen-type</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-specimen-type</t>
   </si>
   <si>
     <t>FiveWs.what[x]</t>
@@ -2130,7 +2130,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="122.17578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="79.2265625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2145,7 +2145,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="115.21875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="100.87890625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="57.9296875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:27:59+00:00</t>
+    <t>2023-05-11T18:29:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:29:46+00:00</t>
+    <t>2023-05-11T18:48:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:48:31+00:00</t>
+    <t>2023-05-11T18:54:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:54:41+00:00</t>
+    <t>2023-05-11T19:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:41:30+00:00</t>
+    <t>2023-05-11T19:42:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:42:15+00:00</t>
+    <t>2023-05-11T20:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:23:29+00:00</t>
+    <t>2023-05-11T20:24:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:24:51+00:00</t>
+    <t>2023-05-12T02:48:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:48:54+00:00</t>
+    <t>2023-05-12T02:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:49:37+00:00</t>
+    <t>2023-05-12T07:30:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:25+00:00</t>
+    <t>2023-05-12T07:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:35+00:00</t>
+    <t>2023-05-12T07:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:36:14+00:00</t>
+    <t>2023-05-12T07:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:36:30+00:00</t>
+    <t>2023-05-12T07:54:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:54:06+00:00</t>
+    <t>2023-05-12T07:55:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:55:51+00:00</t>
+    <t>2023-05-12T10:26:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:26:59+00:00</t>
+    <t>2023-05-12T10:27:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:27:50+00:00</t>
+    <t>2023-05-12T10:32:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:32:06+00:00</t>
+    <t>2023-05-12T10:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:40:31+00:00</t>
+    <t>2023-05-12T13:37:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:37:18+00:00</t>
+    <t>2023-05-12T13:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:51:30+00:00</t>
+    <t>2023-05-23T09:07:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T09:07:38+00:00</t>
+    <t>2023-05-23T09:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
